--- a/docs/StructureDefinition-SpacecraftLifeSupportTelemetry.xlsx
+++ b/docs/StructureDefinition-SpacecraftLifeSupportTelemetry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.6</t>
+    <t>0.5.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-30T19:11:20-07:00</t>
+    <t>2026-02-02T11:11:20-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SpacecraftLifeSupportTelemetry.xlsx
+++ b/docs/StructureDefinition-SpacecraftLifeSupportTelemetry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.8</t>
+    <t>0.5.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T11:11:20-06:00</t>
+    <t>2026-02-04T10:26:00-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SpacecraftLifeSupportTelemetry.xlsx
+++ b/docs/StructureDefinition-SpacecraftLifeSupportTelemetry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.12</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T00:24:16-05:00</t>
+    <t>2026-05-25T15:07:02-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SpacecraftLifeSupportTelemetry.xlsx
+++ b/docs/StructureDefinition-SpacecraftLifeSupportTelemetry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SpacecraftLifeSupportTelemetry.xlsx
+++ b/docs/StructureDefinition-SpacecraftLifeSupportTelemetry.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1951" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="258">
   <si>
     <t>Property</t>
   </si>
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/StructureDefinition/SpacecraftLifeSupportTelemetry</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/SpacecraftLifeSupportTelemetry</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -1046,27 +1049,29 @@
       <c r="A14" t="s" s="2">
         <v>25</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>26</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>3</v>
@@ -1074,26 +1079,26 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1145,112 +1150,112 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2">
@@ -1266,10 +1271,10 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -1281,7 +1286,7 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L2" t="s" s="2">
         <v>9</v>
@@ -1338,13 +1343,13 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
@@ -1355,10 +1360,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1366,10 +1371,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -1381,13 +1386,13 @@
         <v>20</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1438,27 +1443,27 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1466,10 +1471,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -1481,13 +1486,13 @@
         <v>20</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1538,13 +1543,13 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
@@ -1555,21 +1560,21 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
@@ -1581,16 +1586,16 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1628,74 +1633,74 @@
         <v>20</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P6" t="s" s="2">
         <v>20</v>
@@ -1744,27 +1749,27 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1772,10 +1777,10 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -1787,16 +1792,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -1846,13 +1851,13 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
@@ -1863,10 +1868,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1874,10 +1879,10 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -1889,16 +1894,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1948,13 +1953,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -1965,10 +1970,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1976,10 +1981,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -1991,16 +1996,16 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2050,13 +2055,13 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
@@ -2067,10 +2072,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2078,10 +2083,10 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
@@ -2093,16 +2098,16 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2152,13 +2157,13 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>20</v>
@@ -2169,10 +2174,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2180,10 +2185,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
@@ -2195,16 +2200,16 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2254,13 +2259,13 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>20</v>
@@ -2271,10 +2276,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2282,10 +2287,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -2297,16 +2302,16 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2356,13 +2361,13 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
@@ -2373,10 +2378,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2384,10 +2389,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -2399,13 +2404,13 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2456,27 +2461,27 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2484,10 +2489,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -2499,13 +2504,13 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2556,13 +2561,13 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
@@ -2573,21 +2578,21 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -2599,16 +2604,16 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2646,74 +2651,74 @@
         <v>20</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -2762,27 +2767,27 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2790,10 +2795,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -2805,16 +2810,16 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2864,13 +2869,13 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
@@ -2881,10 +2886,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2892,10 +2897,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
@@ -2907,16 +2912,16 @@
         <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2966,13 +2971,13 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
@@ -2983,10 +2988,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2994,10 +2999,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -3009,16 +3014,16 @@
         <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3068,13 +3073,13 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
@@ -3085,10 +3090,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3096,10 +3101,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -3111,16 +3116,16 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3170,13 +3175,13 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
@@ -3187,10 +3192,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3198,10 +3203,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -3213,13 +3218,13 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3270,27 +3275,27 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3298,10 +3303,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -3313,13 +3318,13 @@
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3370,13 +3375,13 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
@@ -3387,21 +3392,21 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -3413,16 +3418,16 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3460,74 +3465,74 @@
         <v>20</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -3576,27 +3581,27 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3604,10 +3609,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -3619,16 +3624,16 @@
         <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -3678,13 +3683,13 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
@@ -3695,10 +3700,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3706,10 +3711,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -3721,16 +3726,16 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -3780,13 +3785,13 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
@@ -3797,10 +3802,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3808,10 +3813,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -3823,16 +3828,16 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -3882,13 +3887,13 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
@@ -3899,10 +3904,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3910,10 +3915,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -3925,16 +3930,16 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -3984,27 +3989,27 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4012,10 +4017,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -4027,13 +4032,13 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4084,13 +4089,13 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
@@ -4101,21 +4106,21 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -4127,16 +4132,16 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4174,74 +4179,74 @@
         <v>20</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -4290,27 +4295,27 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4318,10 +4323,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -4333,13 +4338,13 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4390,13 +4395,13 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
@@ -4407,10 +4412,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4418,10 +4423,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -4433,13 +4438,13 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4490,13 +4495,13 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
@@ -4507,10 +4512,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4518,10 +4523,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -4533,13 +4538,13 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4590,27 +4595,27 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4618,10 +4623,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -4633,13 +4638,13 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4690,13 +4695,13 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
@@ -4707,21 +4712,21 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -4733,16 +4738,16 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -4780,74 +4785,74 @@
         <v>20</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -4896,27 +4901,27 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4924,10 +4929,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -4939,16 +4944,16 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -4998,13 +5003,13 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
@@ -5015,10 +5020,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5026,10 +5031,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -5041,16 +5046,16 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5100,13 +5105,13 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
@@ -5117,10 +5122,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5128,10 +5133,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -5143,16 +5148,16 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5202,13 +5207,13 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
@@ -5219,10 +5224,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5230,10 +5235,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -5245,13 +5250,13 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5302,27 +5307,27 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5330,10 +5335,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
@@ -5345,13 +5350,13 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5402,13 +5407,13 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
@@ -5419,21 +5424,21 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -5445,16 +5450,16 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -5492,74 +5497,74 @@
         <v>20</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -5608,27 +5613,27 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5636,10 +5641,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -5651,16 +5656,16 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -5710,13 +5715,13 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
@@ -5727,10 +5732,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5738,10 +5743,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -5753,16 +5758,16 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -5812,13 +5817,13 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>20</v>
@@ -5829,10 +5834,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5840,10 +5845,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -5855,16 +5860,16 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -5914,13 +5919,13 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>20</v>
@@ -5931,10 +5936,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5942,10 +5947,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
@@ -5957,16 +5962,16 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6016,13 +6021,13 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>20</v>
@@ -6033,10 +6038,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6044,10 +6049,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -6059,13 +6064,13 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6116,27 +6121,27 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6144,10 +6149,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -6159,13 +6164,13 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6216,13 +6221,13 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
@@ -6233,21 +6238,21 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -6259,16 +6264,16 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -6306,74 +6311,74 @@
         <v>20</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -6422,27 +6427,27 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6450,10 +6455,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>20</v>
@@ -6465,16 +6470,16 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -6524,13 +6529,13 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>20</v>
@@ -6541,10 +6546,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6552,10 +6557,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -6567,16 +6572,16 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -6626,13 +6631,13 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>20</v>
@@ -6643,10 +6648,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6654,10 +6659,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -6669,16 +6674,16 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -6728,13 +6733,13 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
@@ -6745,10 +6750,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6756,10 +6761,10 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>20</v>
@@ -6771,16 +6776,16 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -6830,13 +6835,13 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
@@ -6847,10 +6852,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -6858,10 +6863,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>20</v>
@@ -6873,16 +6878,16 @@
         <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -6932,13 +6937,13 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>20</v>
@@ -6949,10 +6954,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -6960,10 +6965,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>20</v>
@@ -6975,13 +6980,13 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7032,13 +7037,13 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>20</v>
@@ -7049,10 +7054,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7060,10 +7065,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>20</v>
@@ -7075,16 +7080,16 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -7134,13 +7139,13 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>20</v>
@@ -7151,10 +7156,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7162,10 +7167,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>20</v>
@@ -7177,13 +7182,13 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7234,13 +7239,13 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>20</v>
